--- a/data/vessels.xlsx
+++ b/data/vessels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38e8c98c8a0534a6/Desktop/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F332942C-A966-4A01-8E54-99FE955C9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{62082F0D-5C52-41F5-9873-153861F45DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7270" xr2:uid="{52C89224-C974-47A4-8542-3B253D90E4DE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{52C89224-C974-47A4-8542-3B253D90E4DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,27 +122,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <start/>
       <end/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <start style="thin">
-        <color rgb="FF000000"/>
-      </start>
-      <end style="thin">
-        <color rgb="FF000000"/>
-      </end>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -151,7 +136,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -486,136 +471,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306B2CDA-46F9-48B8-85CE-FD716999A00C}">
-  <dimension ref="B2:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="2" max="2" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B6" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B8" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B9" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B12" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B13" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B14" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B15" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B16" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="1" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/data/vessels.xlsx
+++ b/data/vessels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38e8c98c8a0534a6/Desktop/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{62082F0D-5C52-41F5-9873-153861F45DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{8CAD7888-5CFC-4381-B238-FD7374CE4776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{52C89224-C974-47A4-8542-3B253D90E4DE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="25" uniqueCount="25">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="26" uniqueCount="26">
   <si>
     <t>CMA CGM Chile</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>ONE Future</t>
+  </si>
+  <si>
+    <t>Vessel Name</t>
   </si>
 </sst>
 </file>
@@ -134,9 +137,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -471,136 +473,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306B2CDA-46F9-48B8-85CE-FD716999A00C}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="36.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>24</v>
       </c>
     </row>
